--- a/output/roomself_excel/1214.xlsx
+++ b/output/roomself_excel/1214.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>610151</v>
+        <v>500648</v>
       </c>
       <c r="D2" t="n">
-        <v>10264</v>
+        <v>7632</v>
       </c>
       <c r="E2" t="n">
-        <v>1538</v>
+        <v>970</v>
       </c>
       <c r="F2" t="n">
-        <v>970</v>
+        <v>683</v>
       </c>
     </row>
     <row r="3">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>116394</v>
+        <v>122760</v>
       </c>
       <c r="D4" t="n">
-        <v>3020</v>
+        <v>2808</v>
       </c>
       <c r="E4" t="n">
-        <v>874</v>
+        <v>382</v>
       </c>
       <c r="F4" t="n">
-        <v>479</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55880</v>
+        <v>119504</v>
       </c>
       <c r="D5" t="n">
-        <v>1896</v>
+        <v>2784</v>
       </c>
       <c r="E5" t="n">
-        <v>302</v>
+        <v>433</v>
       </c>
       <c r="F5" t="n">
-        <v>246</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>70251</v>
+        <v>28690</v>
       </c>
       <c r="D7" t="n">
-        <v>3060</v>
+        <v>1404</v>
       </c>
       <c r="E7" t="n">
-        <v>694</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28690</v>
+        <v>109503</v>
       </c>
       <c r="D8" t="n">
-        <v>1404</v>
+        <v>3276</v>
       </c>
       <c r="E8" t="n">
-        <v>429</v>
+        <v>44</v>
       </c>
       <c r="F8" t="n">
-        <v>271</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>42680</v>
+        <v>32508</v>
       </c>
       <c r="D9" t="n">
-        <v>1656</v>
+        <v>1444</v>
       </c>
       <c r="E9" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>122760</v>
+        <v>42680</v>
       </c>
       <c r="D10" t="n">
-        <v>2808</v>
+        <v>1656</v>
       </c>
       <c r="E10" t="n">
-        <v>382</v>
+        <v>194</v>
       </c>
       <c r="F10" t="n">
-        <v>377</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>55480</v>
+        <v>31126</v>
       </c>
       <c r="D11" t="n">
-        <v>2068</v>
+        <v>1420</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>320911</v>
+        <v>363823</v>
       </c>
       <c r="D12" t="n">
-        <v>5104</v>
+        <v>4034</v>
       </c>
       <c r="E12" t="n">
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>826</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>32508</v>
+        <v>116394</v>
       </c>
       <c r="D13" t="n">
-        <v>1444</v>
+        <v>3020</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25456</v>
+        <v>55880</v>
       </c>
       <c r="D14" t="n">
-        <v>1280</v>
+        <v>1896</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>302</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>33220</v>
+        <v>70251</v>
       </c>
       <c r="D15" t="n">
-        <v>1484</v>
+        <v>3060</v>
       </c>
       <c r="E15" t="n">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="F15" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>119504</v>
+        <v>55480</v>
       </c>
       <c r="D16" t="n">
-        <v>2784</v>
+        <v>2068</v>
       </c>
       <c r="E16" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>31126</v>
+        <v>320911</v>
       </c>
       <c r="D17" t="n">
-        <v>1420</v>
+        <v>5104</v>
       </c>
       <c r="E17" t="n">
-        <v>566</v>
+        <v>769</v>
       </c>
       <c r="F17" t="n">
-        <v>420</v>
+        <v>603</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>363823</v>
+        <v>25456</v>
       </c>
       <c r="D18" t="n">
-        <v>4034</v>
+        <v>1280</v>
       </c>
       <c r="E18" t="n">
-        <v>390</v>
+        <v>46</v>
       </c>
       <c r="F18" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -844,15 +844,37 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>33220</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1484</v>
+      </c>
+      <c r="E19" t="n">
+        <v>246</v>
+      </c>
+      <c r="F19" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>64722</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D20" t="n">
         <v>2252</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E20" t="n">
         <v>670</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F20" t="n">
         <v>209</v>
       </c>
     </row>

--- a/output/roomself_excel/1214.xlsx
+++ b/output/roomself_excel/1214.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,11 +510,38 @@
       <c r="D2" t="n">
         <v>7632</v>
       </c>
-      <c r="E2" t="n">
-        <v>970</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>683</v>
+        <v>778</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>592</v>
+      </c>
+      <c r="J2" t="n">
+        <v>47</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>638</v>
+      </c>
+      <c r="M2" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +559,31 @@
       <c r="D3" t="n">
         <v>2972</v>
       </c>
-      <c r="E3" t="n">
-        <v>462</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>377</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="G3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>414</v>
+      </c>
+      <c r="J3" t="n">
+        <v>48</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +600,31 @@
       <c r="D4" t="n">
         <v>2808</v>
       </c>
-      <c r="E4" t="n">
-        <v>382</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>377</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="G4" t="n">
+        <v>47</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>330</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +641,31 @@
       <c r="D5" t="n">
         <v>2784</v>
       </c>
-      <c r="E5" t="n">
-        <v>433</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>290</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="G5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>255</v>
+      </c>
+      <c r="J5" t="n">
+        <v>45</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +682,23 @@
       <c r="D6" t="n">
         <v>2288</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>352</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>26</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +715,15 @@
       <c r="D7" t="n">
         <v>1404</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +740,15 @@
       <c r="D8" t="n">
         <v>3276</v>
       </c>
-      <c r="E8" t="n">
-        <v>44</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +765,15 @@
       <c r="D9" t="n">
         <v>1444</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +790,23 @@
       <c r="D10" t="n">
         <v>1656</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>194</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>26</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +823,31 @@
       <c r="D11" t="n">
         <v>1420</v>
       </c>
-      <c r="E11" t="n">
-        <v>390</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>206</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="G11" t="n">
+        <v>48</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>124</v>
+      </c>
+      <c r="J11" t="n">
+        <v>48</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +864,15 @@
       <c r="D12" t="n">
         <v>4034</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +889,23 @@
       <c r="D13" t="n">
         <v>3020</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>223</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>48</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +922,31 @@
       <c r="D14" t="n">
         <v>1896</v>
       </c>
-      <c r="E14" t="n">
-        <v>302</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>246</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="G14" t="n">
+        <v>48</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>254</v>
+      </c>
+      <c r="J14" t="n">
+        <v>26</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +963,23 @@
       <c r="D15" t="n">
         <v>3060</v>
       </c>
-      <c r="E15" t="n">
-        <v>204</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>204</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="G15" t="n">
+        <v>48</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +996,23 @@
       <c r="D16" t="n">
         <v>2068</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="G16" t="n">
+        <v>24</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,11 +1029,38 @@
       <c r="D17" t="n">
         <v>5104</v>
       </c>
-      <c r="E17" t="n">
-        <v>769</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>603</v>
+        <v>108</v>
+      </c>
+      <c r="G17" t="n">
+        <v>48</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>555</v>
+      </c>
+      <c r="J17" t="n">
+        <v>48</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>99</v>
+      </c>
+      <c r="M17" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="18">
@@ -827,12 +1078,23 @@
       <c r="D18" t="n">
         <v>1280</v>
       </c>
-      <c r="E18" t="n">
-        <v>46</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="G18" t="n">
+        <v>24</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1111,31 @@
       <c r="D19" t="n">
         <v>1484</v>
       </c>
-      <c r="E19" t="n">
-        <v>246</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>195</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="G19" t="n">
+        <v>26</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>220</v>
+      </c>
+      <c r="J19" t="n">
+        <v>44</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1152,31 @@
       <c r="D20" t="n">
         <v>2252</v>
       </c>
-      <c r="E20" t="n">
-        <v>670</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>209</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="G20" t="n">
+        <v>48</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>402</v>
+      </c>
+      <c r="J20" t="n">
+        <v>48</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/1214.xlsx
+++ b/output/roomself_excel/1214.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,66 @@
           <t>ExtWallWidth_3</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -543,6 +603,54 @@
       <c r="M2" t="n">
         <v>24</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>527</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>45</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>93</v>
+      </c>
+      <c r="U2" t="n">
+        <v>45</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -584,6 +692,54 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>48</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>94</v>
+      </c>
+      <c r="U3" t="n">
+        <v>48</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -625,6 +781,42 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>47</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>198</v>
+      </c>
+      <c r="U4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -666,6 +858,42 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>35</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>170</v>
+      </c>
+      <c r="U5" t="n">
+        <v>45</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -699,6 +927,18 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -724,6 +964,18 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -749,6 +1001,18 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -774,6 +1038,18 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -807,6 +1083,18 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -848,6 +1136,18 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -873,6 +1173,18 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -906,6 +1218,30 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>48</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -947,6 +1283,30 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>48</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -980,6 +1340,30 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>48</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1013,6 +1397,18 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1062,6 +1458,42 @@
       <c r="M17" t="n">
         <v>44</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>48</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>170</v>
+      </c>
+      <c r="U17" t="n">
+        <v>48</v>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1095,6 +1527,18 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1136,6 +1580,18 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1177,6 +1633,18 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
